--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.6934104164852</v>
+        <v>6.775179192678845</v>
       </c>
       <c r="D2" t="n">
-        <v>43.00919715452136</v>
+        <v>6.988994537609721</v>
       </c>
       <c r="E2" t="n">
-        <v>7.95290174865193</v>
+        <v>1.292346534155938</v>
       </c>
       <c r="F2" t="n">
-        <v>8.177676628211476</v>
+        <v>1.328872452084365</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.41204647128059</v>
+        <v>6.404457551583096</v>
       </c>
       <c r="D3" t="n">
-        <v>40.81967810809279</v>
+        <v>6.633197692565078</v>
       </c>
       <c r="E3" t="n">
-        <v>7.95290174865193</v>
+        <v>1.292346534155938</v>
       </c>
       <c r="F3" t="n">
-        <v>8.177676628211476</v>
+        <v>1.328872452084365</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.09473168765784</v>
+        <v>5.865393899244399</v>
       </c>
       <c r="D4" t="n">
-        <v>36.94395700987573</v>
+        <v>6.003393014104806</v>
       </c>
       <c r="E4" t="n">
-        <v>7.95290174865193</v>
+        <v>1.292346534155938</v>
       </c>
       <c r="F4" t="n">
-        <v>8.177676628211476</v>
+        <v>1.328872452084365</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.6222302157914</v>
+        <v>4.813612410066104</v>
       </c>
       <c r="D5" t="n">
-        <v>30.23791667474018</v>
+        <v>4.913661459645279</v>
       </c>
       <c r="E5" t="n">
-        <v>7.95290174865193</v>
+        <v>1.292346534155938</v>
       </c>
       <c r="F5" t="n">
-        <v>8.177676628211476</v>
+        <v>1.328872452084365</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.72994210431408</v>
+        <v>4.668615591951038</v>
       </c>
       <c r="D6" t="n">
-        <v>30.12945864361069</v>
+        <v>4.896037029586736</v>
       </c>
       <c r="E6" t="n">
-        <v>7.95290174865193</v>
+        <v>1.292346534155938</v>
       </c>
       <c r="F6" t="n">
-        <v>8.177676628211476</v>
+        <v>1.328872452084365</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.51370198150691</v>
+        <v>3.495976571994872</v>
       </c>
       <c r="D7" t="n">
-        <v>22.4126952294456</v>
+        <v>3.642062974784909</v>
       </c>
       <c r="E7" t="n">
-        <v>7.95290174865193</v>
+        <v>1.292346534155938</v>
       </c>
       <c r="F7" t="n">
-        <v>8.177676628211476</v>
+        <v>1.328872452084365</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.79141111012284</v>
+        <v>5.491104305394961</v>
       </c>
       <c r="D8" t="n">
-        <v>35.10808634617446</v>
+        <v>5.70506403125335</v>
       </c>
       <c r="E8" t="n">
-        <v>7.95290174865193</v>
+        <v>1.292346534155938</v>
       </c>
       <c r="F8" t="n">
-        <v>8.177676628211476</v>
+        <v>1.328872452084365</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.38451864488697</v>
+        <v>5.099984279794132</v>
       </c>
       <c r="D9" t="n">
-        <v>30.43672776341034</v>
+        <v>4.94596826155418</v>
       </c>
       <c r="E9" t="n">
-        <v>7.95290174865193</v>
+        <v>1.292346534155938</v>
       </c>
       <c r="F9" t="n">
-        <v>8.177676628211476</v>
+        <v>1.328872452084365</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.07824154319722</v>
+        <v>2.450214250769549</v>
       </c>
       <c r="D10" t="n">
-        <v>15.59797058759588</v>
+        <v>2.534670220484331</v>
       </c>
       <c r="E10" t="n">
-        <v>7.95290174865193</v>
+        <v>1.292346534155938</v>
       </c>
       <c r="F10" t="n">
-        <v>8.177676628211476</v>
+        <v>1.328872452084365</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
